--- a/data/dividends_info_20260417.xlsx
+++ b/data/dividends_info_20260417.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35.29000091552734</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2550297468550097</v>
+        <v>0.2418704708798449</v>
       </c>
       <c r="J2" t="n">
         <v>332</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.45000076293945</v>
+        <v>56.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.262398539889384</v>
+        <v>1.23565751305448</v>
       </c>
       <c r="J3" t="n">
         <v>311</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J4" t="n">
         <v>241</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35.30500030517578</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2549213970316999</v>
+        <v>0.2418704708798449</v>
       </c>
       <c r="J6" t="n">
         <v>241</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.105000019073486</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I7" t="n">
-        <v>3.65795721151069</v>
+        <v>3.640661922118176</v>
       </c>
       <c r="J7" t="n">
         <v>220</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35.30500030517578</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2549213970316999</v>
+        <v>0.2418704708798449</v>
       </c>
       <c r="J11" t="n">
         <v>157</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.199999809265137</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I13" t="n">
-        <v>4.032258188563261</v>
+        <v>4.125412580207591</v>
       </c>
       <c r="J13" t="n">
         <v>101</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.736000061035156</v>
+        <v>9.72700023651123</v>
       </c>
       <c r="I14" t="n">
-        <v>2.670501215797611</v>
+        <v>2.672972074412675</v>
       </c>
       <c r="J14" t="n">
         <v>94</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.39999961853027</v>
+        <v>16.6200008392334</v>
       </c>
       <c r="I15" t="n">
-        <v>3.658536670464694</v>
+        <v>3.610108120955276</v>
       </c>
       <c r="J15" t="n">
         <v>94</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.659999847412109</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I18" t="n">
-        <v>2.120141399913057</v>
+        <v>2.090592417856904</v>
       </c>
       <c r="J18" t="n">
         <v>87</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.399999618530273</v>
+        <v>9.850000381469727</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5319149152031317</v>
+        <v>0.5076141935391424</v>
       </c>
       <c r="J19" t="n">
         <v>87</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.180000066757202</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I20" t="n">
-        <v>3.899082449407415</v>
+        <v>3.863636279894303</v>
       </c>
       <c r="J20" t="n">
         <v>80</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>35.45000076293945</v>
+        <v>35.54999923706055</v>
       </c>
       <c r="I22" t="n">
-        <v>0.423131161556461</v>
+        <v>0.4219409373253273</v>
       </c>
       <c r="J22" t="n">
         <v>80</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.949999809265137</v>
+        <v>5.75</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6722689291134659</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="J23" t="n">
         <v>73</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22.52000045776367</v>
+        <v>22.54000091552734</v>
       </c>
       <c r="I24" t="n">
-        <v>1.110124311359921</v>
+        <v>1.10913926284617</v>
       </c>
       <c r="J24" t="n">
         <v>66</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>26.25</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7276119610120848</v>
       </c>
       <c r="J25" t="n">
         <v>66</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.840000033378601</v>
+        <v>1.889999985694885</v>
       </c>
       <c r="I26" t="n">
-        <v>1.793478228334894</v>
+        <v>1.746031759247188</v>
       </c>
       <c r="J26" t="n">
         <v>66</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.107500076293945</v>
+        <v>5.175000190734863</v>
       </c>
       <c r="I27" t="n">
-        <v>5.677924535841162</v>
+        <v>5.603864527758002</v>
       </c>
       <c r="J27" t="n">
         <v>66</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.073999881744385</v>
+        <v>4.093999862670898</v>
       </c>
       <c r="I28" t="n">
-        <v>3.927344247528354</v>
+        <v>3.90815841150559</v>
       </c>
       <c r="J28" t="n">
         <v>66</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.559999942779541</v>
+        <v>2.584000110626221</v>
       </c>
       <c r="I29" t="n">
-        <v>5.41406262101373</v>
+        <v>5.36377686014924</v>
       </c>
       <c r="J29" t="n">
         <v>66</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>58.59999847412109</v>
+        <v>57.68999862670898</v>
       </c>
       <c r="I30" t="n">
-        <v>1.07508535222611</v>
+        <v>1.092043707743002</v>
       </c>
       <c r="J30" t="n">
         <v>66</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>19.10000038146973</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I31" t="n">
-        <v>4.08376955194584</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J31" t="n">
         <v>66</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>22.09000015258789</v>
+        <v>22.46999931335449</v>
       </c>
       <c r="I32" t="n">
-        <v>3.84789494852231</v>
+        <v>3.78282165542757</v>
       </c>
       <c r="J32" t="n">
         <v>66</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>35.30500030517578</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2549213970316999</v>
+        <v>0.2418704708798449</v>
       </c>
       <c r="J33" t="n">
         <v>66</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.638000011444092</v>
+        <v>6.527999877929688</v>
       </c>
       <c r="I34" t="n">
-        <v>2.731244345999305</v>
+        <v>2.777267208796243</v>
       </c>
       <c r="J34" t="n">
         <v>66</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.409999847412109</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>3.091557725533207</v>
+        <v>3.030303057248692</v>
       </c>
       <c r="J35" t="n">
         <v>66</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10.08500003814697</v>
+        <v>9.98799991607666</v>
       </c>
       <c r="I36" t="n">
-        <v>2.746653435322111</v>
+        <v>2.773328016894969</v>
       </c>
       <c r="J36" t="n">
         <v>66</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1.210000038146973</v>
+        <v>1.230000019073486</v>
       </c>
       <c r="I37" t="n">
-        <v>1.115702444164735</v>
+        <v>1.097560958589989</v>
       </c>
       <c r="J37" t="n">
         <v>59</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>4.217999935150146</v>
+        <v>4.138000011444092</v>
       </c>
       <c r="I38" t="n">
-        <v>2.607871069018506</v>
+        <v>2.658289021164402</v>
       </c>
       <c r="J38" t="n">
         <v>59</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.700000047683716</v>
+        <v>2.559999942779541</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8888888731905467</v>
+        <v>0.9375000209547584</v>
       </c>
       <c r="J39" t="n">
         <v>59</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>28.14999961853027</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I40" t="n">
-        <v>3.943161687538076</v>
+        <v>3.881118829352121</v>
       </c>
       <c r="J40" t="n">
         <v>48</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.9049999713897705</v>
+        <v>0.9070000052452087</v>
       </c>
       <c r="I41" t="n">
-        <v>3.314917231868003</v>
+        <v>3.307607478115665</v>
       </c>
       <c r="J41" t="n">
         <v>45</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.5320000052452087</v>
+        <v>0.5289999842643738</v>
       </c>
       <c r="I42" t="n">
-        <v>4.323308228051402</v>
+        <v>4.347826216286896</v>
       </c>
       <c r="J42" t="n">
         <v>45</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>18.89999961853027</v>
+        <v>19</v>
       </c>
       <c r="I43" t="n">
-        <v>3.174603238678043</v>
+        <v>3.157894736842105</v>
       </c>
       <c r="J43" t="n">
         <v>45</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.979999542236328</v>
+        <v>9</v>
       </c>
       <c r="I44" t="n">
-        <v>2.227171605736999</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="J44" t="n">
         <v>45</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2.704999923706055</v>
+        <v>2.714999914169312</v>
       </c>
       <c r="I45" t="n">
-        <v>6.654343995447748</v>
+        <v>6.629834463736007</v>
       </c>
       <c r="J45" t="n">
         <v>38</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>8.5</v>
+        <v>8.949999809265137</v>
       </c>
       <c r="I46" t="n">
-        <v>3.529411764705882</v>
+        <v>3.35195537869662</v>
       </c>
       <c r="J46" t="n">
         <v>38</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>13.25</v>
+        <v>13.72999954223633</v>
       </c>
       <c r="I47" t="n">
-        <v>1.886792452830189</v>
+        <v>1.820830359323379</v>
       </c>
       <c r="J47" t="n">
         <v>38</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>3.380000114440918</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8875739344453326</v>
+        <v>0.8955224135533352</v>
       </c>
       <c r="J48" t="n">
         <v>38</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13.10000038146973</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I50" t="n">
-        <v>4.427480787103062</v>
+        <v>4.360902193099543</v>
       </c>
       <c r="J50" t="n">
         <v>38</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.404000043869019</v>
+        <v>2.394000053405762</v>
       </c>
       <c r="I51" t="n">
-        <v>4.326123049175219</v>
+        <v>4.344193720967011</v>
       </c>
       <c r="J51" t="n">
         <v>31</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10</v>
+        <v>10.11999988555908</v>
       </c>
       <c r="I52" t="n">
-        <v>2.9</v>
+        <v>2.865612680626813</v>
       </c>
       <c r="J52" t="n">
         <v>31</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2.109999895095825</v>
+        <v>2.115000009536743</v>
       </c>
       <c r="I53" t="n">
-        <v>3.649289280960038</v>
+        <v>3.640661922118176</v>
       </c>
       <c r="J53" t="n">
         <v>31</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>37.13000106811523</v>
+        <v>37.5099983215332</v>
       </c>
       <c r="I54" t="n">
-        <v>4.416913419936102</v>
+        <v>4.372167617662974</v>
       </c>
       <c r="J54" t="n">
         <v>31</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>36.25</v>
+        <v>37.41999816894531</v>
       </c>
       <c r="I55" t="n">
-        <v>5.517241379310345</v>
+        <v>5.344735697127295</v>
       </c>
       <c r="J55" t="n">
         <v>31</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>4.02400016784668</v>
+        <v>4.105999946594238</v>
       </c>
       <c r="I56" t="n">
-        <v>2.485089359564116</v>
+        <v>2.435460333674529</v>
       </c>
       <c r="J56" t="n">
         <v>31</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>37.27000045776367</v>
+        <v>36.75</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3983364587511682</v>
+        <v>0.4039727891156463</v>
       </c>
       <c r="J57" t="n">
         <v>31</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>22.84000015258789</v>
+        <v>23.70000076293945</v>
       </c>
       <c r="I58" t="n">
-        <v>4.028020988851698</v>
+        <v>3.88185641512146</v>
       </c>
       <c r="J58" t="n">
         <v>31</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>8.319999694824219</v>
+        <v>8.595000267028809</v>
       </c>
       <c r="I59" t="n">
-        <v>3.605769363028063</v>
+        <v>3.490401287721036</v>
       </c>
       <c r="J59" t="n">
         <v>31</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>85.09999847412109</v>
+        <v>87.83999633789062</v>
       </c>
       <c r="I60" t="n">
-        <v>1.222091678786885</v>
+        <v>1.183970905462556</v>
       </c>
       <c r="J60" t="n">
         <v>31</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>47.77000045776367</v>
+        <v>50.34000015258789</v>
       </c>
       <c r="I61" t="n">
-        <v>1.465354811162106</v>
+        <v>1.390544294553432</v>
       </c>
       <c r="J61" t="n">
         <v>31</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>55.45000076293945</v>
+        <v>56.65000152587891</v>
       </c>
       <c r="I62" t="n">
-        <v>3.967538268223779</v>
+        <v>3.883495041028365</v>
       </c>
       <c r="J62" t="n">
         <v>31</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>8.899999618530273</v>
+        <v>9.16100025177002</v>
       </c>
       <c r="I63" t="n">
-        <v>9.662921762484508</v>
+        <v>9.387621180709358</v>
       </c>
       <c r="J63" t="n">
         <v>31</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.10599994659424</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="I64" t="n">
-        <v>4.625805406165924</v>
+        <v>4.516129171190852</v>
       </c>
       <c r="J64" t="n">
         <v>31</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.049999952316284</v>
+        <v>2.130000114440918</v>
       </c>
       <c r="I65" t="n">
-        <v>1.95121955758117</v>
+        <v>1.877934171402577</v>
       </c>
       <c r="J65" t="n">
         <v>31</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>9</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I66" t="n">
-        <v>3.333333333333333</v>
+        <v>3.205128322691611</v>
       </c>
       <c r="J66" t="n">
         <v>31</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.25</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I67" t="n">
-        <v>4.8</v>
+        <v>4.757709291077578</v>
       </c>
       <c r="J67" t="n">
         <v>31</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>74</v>
+        <v>74.5</v>
       </c>
       <c r="I68" t="n">
-        <v>2.783783783783784</v>
+        <v>2.76510067114094</v>
       </c>
       <c r="J68" t="n">
         <v>31</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>15.4399995803833</v>
+        <v>15.85000038146973</v>
       </c>
       <c r="I69" t="n">
-        <v>4.857513085381711</v>
+        <v>4.731861084854148</v>
       </c>
       <c r="J69" t="n">
         <v>31</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>15.94999980926514</v>
+        <v>16.53000068664551</v>
       </c>
       <c r="I70" t="n">
-        <v>1.880877765438806</v>
+        <v>1.814881957278854</v>
       </c>
       <c r="J70" t="n">
         <v>31</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>45.90000152587891</v>
+        <v>46</v>
       </c>
       <c r="I71" t="n">
-        <v>1.851851790289726</v>
+        <v>1.847826086956522</v>
       </c>
       <c r="J71" t="n">
         <v>31</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>34.04000091552734</v>
+        <v>34.70000076293945</v>
       </c>
       <c r="I72" t="n">
-        <v>2.497062212510907</v>
+        <v>2.449567669484962</v>
       </c>
       <c r="J72" t="n">
         <v>31</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>62.97999954223633</v>
+        <v>63.27999877929688</v>
       </c>
       <c r="I73" t="n">
-        <v>2.064147363367604</v>
+        <v>2.054361607265576</v>
       </c>
       <c r="J73" t="n">
         <v>31</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>7.920000076293945</v>
+        <v>8</v>
       </c>
       <c r="I74" t="n">
-        <v>7.575757502779743</v>
+        <v>7.5</v>
       </c>
       <c r="J74" t="n">
         <v>31</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>6.099999904632568</v>
+        <v>6</v>
       </c>
       <c r="I75" t="n">
-        <v>7.704918153245615</v>
+        <v>7.833333333333332</v>
       </c>
       <c r="J75" t="n">
         <v>31</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>21.5</v>
+        <v>20.95999908447266</v>
       </c>
       <c r="I77" t="n">
-        <v>4.651162790697675</v>
+        <v>4.770992574807927</v>
       </c>
       <c r="J77" t="n">
         <v>31</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>4.789999961853027</v>
+        <v>4.849999904632568</v>
       </c>
       <c r="I78" t="n">
-        <v>4.488517781048719</v>
+        <v>4.432989777889247</v>
       </c>
       <c r="J78" t="n">
         <v>31</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>23.40500068664551</v>
+        <v>21.76000022888184</v>
       </c>
       <c r="I79" t="n">
-        <v>1.1535996243489</v>
+        <v>1.240808810478006</v>
       </c>
       <c r="J79" t="n">
         <v>31</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.060000419616699</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I80" t="n">
-        <v>2.481389448978605</v>
+        <v>2.469135686185122</v>
       </c>
       <c r="J80" t="n">
         <v>31</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>9.520000457763672</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="I81" t="n">
-        <v>2.521008282140125</v>
+        <v>2.513088955043594</v>
       </c>
       <c r="J81" t="n">
         <v>31</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>22.06999969482422</v>
+        <v>22.43000030517578</v>
       </c>
       <c r="I82" t="n">
-        <v>3.579519759509866</v>
+        <v>3.52206861012706</v>
       </c>
       <c r="J82" t="n">
         <v>31</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>4.710000038146973</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="I83" t="n">
-        <v>1.974522277001688</v>
+        <v>1.93749992301067</v>
       </c>
       <c r="J83" t="n">
         <v>31</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>37.70000076293945</v>
+        <v>38.68000030517578</v>
       </c>
       <c r="I85" t="n">
-        <v>0.9283819440769439</v>
+        <v>0.9048603858288139</v>
       </c>
       <c r="J85" t="n">
         <v>31</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>7.289999961853027</v>
+        <v>7.385000228881836</v>
       </c>
       <c r="I86" t="n">
-        <v>7.603566569280254</v>
+        <v>7.505754675974149</v>
       </c>
       <c r="J86" t="n">
         <v>31</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2.200000047683716</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I87" t="n">
-        <v>2.727272668160684</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J87" t="n">
         <v>31</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>12.75</v>
+        <v>12.94999980926514</v>
       </c>
       <c r="I88" t="n">
-        <v>1.568627450980392</v>
+        <v>1.544401567148357</v>
       </c>
       <c r="J88" t="n">
         <v>31</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.105000019073486</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I89" t="n">
-        <v>1.687141681870651</v>
+        <v>1.661290373688063</v>
       </c>
       <c r="J89" t="n">
         <v>31</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.757999897003174</v>
+        <v>5.922999858856201</v>
       </c>
       <c r="I90" t="n">
-        <v>3.299756919045587</v>
+        <v>3.207833944414295</v>
       </c>
       <c r="J90" t="n">
         <v>31</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>10.33500003814697</v>
+        <v>10.34500026702881</v>
       </c>
       <c r="I91" t="n">
-        <v>4.179970956995333</v>
+        <v>4.175930293369387</v>
       </c>
       <c r="J91" t="n">
         <v>31</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>27.18000030517578</v>
+        <v>27.77000045776367</v>
       </c>
       <c r="I92" t="n">
-        <v>1.618837362250554</v>
+        <v>1.584443618102242</v>
       </c>
       <c r="J92" t="n">
         <v>31</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1.139999985694885</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I93" t="n">
-        <v>2.631578980390385</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J93" t="n">
         <v>31</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>8.470000267028809</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I94" t="n">
-        <v>5.548996283147359</v>
+        <v>5.497075900762102</v>
       </c>
       <c r="J94" t="n">
         <v>31</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>56.02000045776367</v>
+        <v>56.79999923706055</v>
       </c>
       <c r="I95" t="n">
-        <v>2.499107441199561</v>
+        <v>2.464788765501489</v>
       </c>
       <c r="J95" t="n">
         <v>31</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3.604000091552734</v>
+        <v>3.611000061035156</v>
       </c>
       <c r="I96" t="n">
-        <v>8.324084139263967</v>
+        <v>8.307947796433982</v>
       </c>
       <c r="J96" t="n">
         <v>31</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>13</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="I97" t="n">
-        <v>0.923076923076923</v>
+        <v>0.8988763788094286</v>
       </c>
       <c r="J97" t="n">
         <v>31</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>3.490000009536743</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I98" t="n">
-        <v>4.871060158609155</v>
+        <v>4.970760123029561</v>
       </c>
       <c r="J98" t="n">
         <v>31</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>21.35000038146973</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="I99" t="n">
-        <v>3.278688466008412</v>
+        <v>3.286385094240039</v>
       </c>
       <c r="J99" t="n">
         <v>31</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.559999942779541</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="I100" t="n">
-        <v>1.367187530559023</v>
+        <v>1.33587792094622</v>
       </c>
       <c r="J100" t="n">
         <v>31</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6.110000133514404</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I101" t="n">
-        <v>5.400981878705585</v>
+        <v>5.383360421520929</v>
       </c>
       <c r="J101" t="n">
         <v>31</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.984000027179718</v>
+        <v>0.9750000238418579</v>
       </c>
       <c r="I102" t="n">
-        <v>7.113820941715806</v>
+        <v>7.179487003925837</v>
       </c>
       <c r="J102" t="n">
         <v>31</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>50.20000076293945</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="I103" t="n">
-        <v>1.414342607986897</v>
+        <v>1.408730116080326</v>
       </c>
       <c r="J103" t="n">
         <v>31</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>94.09999847412109</v>
+        <v>96</v>
       </c>
       <c r="I104" t="n">
-        <v>1.434644019012679</v>
+        <v>1.40625</v>
       </c>
       <c r="J104" t="n">
         <v>31</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>7.139999866485596</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I105" t="n">
-        <v>1.120448200223526</v>
+        <v>1.123595523677711</v>
       </c>
       <c r="J105" t="n">
         <v>31</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4.063000202178955</v>
+        <v>3.872999906539917</v>
       </c>
       <c r="I107" t="n">
-        <v>4.184100210205019</v>
+        <v>4.389362357405156</v>
       </c>
       <c r="J107" t="n">
         <v>31</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>57.40000152587891</v>
+        <v>58.5</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7839721045950089</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="J109" t="n">
         <v>31</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>4.849999904632568</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8247422842584647</v>
+        <v>0.823045244878931</v>
       </c>
       <c r="J110" t="n">
         <v>31</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>33.95999908447266</v>
+        <v>35.47999954223633</v>
       </c>
       <c r="I111" t="n">
-        <v>3.091872874873208</v>
+        <v>2.95941379241015</v>
       </c>
       <c r="J111" t="n">
         <v>31</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>19.40999984741211</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="I113" t="n">
-        <v>1.957753750578543</v>
+        <v>1.900950497003153</v>
       </c>
       <c r="J113" t="n">
         <v>31</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>24.88999938964844</v>
+        <v>24.42000007629395</v>
       </c>
       <c r="I114" t="n">
-        <v>2.410606728457918</v>
+        <v>2.457002449326191</v>
       </c>
       <c r="J114" t="n">
         <v>31</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>34.65000152587891</v>
+        <v>35.65000152587891</v>
       </c>
       <c r="I115" t="n">
-        <v>1.010100965619285</v>
+        <v>0.9817671389044105</v>
       </c>
       <c r="J115" t="n">
         <v>31</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>3.5</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4857142857142858</v>
+        <v>0.482954548071485</v>
       </c>
       <c r="J116" t="n">
         <v>31</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>2.865000009536743</v>
+        <v>2.869999885559082</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3490401384542038</v>
+        <v>0.3484320696428174</v>
       </c>
       <c r="J117" t="n">
         <v>31</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>22.20000076293945</v>
+        <v>22.54999923706055</v>
       </c>
       <c r="I118" t="n">
-        <v>5.045044871663794</v>
+        <v>4.966740744537582</v>
       </c>
       <c r="J118" t="n">
         <v>31</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1.509999990463257</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I119" t="n">
-        <v>6.622516598117379</v>
+        <v>6.369426538796359</v>
       </c>
       <c r="J119" t="n">
         <v>31</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>2.619999885559082</v>
+        <v>2.696000099182129</v>
       </c>
       <c r="I120" t="n">
-        <v>9.923664555600489</v>
+        <v>9.643916559160173</v>
       </c>
       <c r="J120" t="n">
         <v>31</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>2.437999963760376</v>
+        <v>2.444000005722046</v>
       </c>
       <c r="I121" t="n">
-        <v>3.785890130106331</v>
+        <v>3.776595735838848</v>
       </c>
       <c r="J121" t="n">
         <v>31</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>9.199999809265137</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I122" t="n">
-        <v>3.804347904958889</v>
+        <v>3.739316376473546</v>
       </c>
       <c r="J122" t="n">
         <v>24</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>5.199999809265137</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I123" t="n">
-        <v>1.846153913870368</v>
+        <v>1.927710835990328</v>
       </c>
       <c r="J123" t="n">
         <v>24</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>11.89999961853027</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I125" t="n">
-        <v>1.680672322783665</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J125" t="n">
         <v>24</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9.100000381469727</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I126" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J126" t="n">
         <v>24</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>16.31999969482422</v>
+        <v>16.54000091552734</v>
       </c>
       <c r="I128" t="n">
-        <v>3.063725547486203</v>
+        <v>3.022974439684658</v>
       </c>
       <c r="J128" t="n">
         <v>24</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>3.980000019073486</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="I129" t="n">
-        <v>2.512562802029314</v>
+        <v>2.475247548124555</v>
       </c>
       <c r="J129" t="n">
         <v>24</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>4.650000095367432</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="I132" t="n">
-        <v>2.04301071078781</v>
+        <v>2.056277107212606</v>
       </c>
       <c r="J132" t="n">
         <v>24</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.320000052452087</v>
+        <v>1.350000023841858</v>
       </c>
       <c r="I133" t="n">
-        <v>2.272727182417209</v>
+        <v>2.222222182976366</v>
       </c>
       <c r="J133" t="n">
         <v>24</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>7.199999809265137</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="I136" t="n">
-        <v>3.055555636500137</v>
+        <v>3.005464410393148</v>
       </c>
       <c r="J136" t="n">
         <v>24</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>3.430000066757202</v>
+        <v>3.464999914169312</v>
       </c>
       <c r="I137" t="n">
-        <v>4.664722941281676</v>
+        <v>4.617604731986203</v>
       </c>
       <c r="J137" t="n">
         <v>17</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>23.14999961853027</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I138" t="n">
-        <v>2.634989244283742</v>
+        <v>2.723214332090349</v>
       </c>
       <c r="J138" t="n">
         <v>17</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>9.300000190734863</v>
+        <v>9.550000190734863</v>
       </c>
       <c r="I141" t="n">
-        <v>5.489247199248299</v>
+        <v>5.345549631457311</v>
       </c>
       <c r="J141" t="n">
         <v>17</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>7.699999809265137</v>
+        <v>7.664999961853027</v>
       </c>
       <c r="I142" t="n">
-        <v>3.506493593352023</v>
+        <v>3.522504909898617</v>
       </c>
       <c r="J142" t="n">
         <v>17</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>5.849999904632568</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I143" t="n">
-        <v>5.982906080440066</v>
+        <v>5.882353129742826</v>
       </c>
       <c r="J143" t="n">
         <v>17</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>18.89999961853027</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="I145" t="n">
-        <v>3.968254048347555</v>
+        <v>3.97877976032976</v>
       </c>
       <c r="J145" t="n">
         <v>17</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>10.44999980926514</v>
+        <v>10.69999980926514</v>
       </c>
       <c r="I146" t="n">
-        <v>4.114832610989668</v>
+        <v>4.01869166042099</v>
       </c>
       <c r="J146" t="n">
         <v>17</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.349999904632568</v>
+        <v>4.394999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>3.448275937667407</v>
+        <v>3.412969298088105</v>
       </c>
       <c r="J147" t="n">
         <v>17</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>12.27999973297119</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="I148" t="n">
-        <v>1.605610784099702</v>
+        <v>1.597803870031967</v>
       </c>
       <c r="J148" t="n">
         <v>17</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>29.45000076293945</v>
+        <v>30</v>
       </c>
       <c r="I149" t="n">
-        <v>3.735144215630259</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="J149" t="n">
         <v>17</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>82.30000305175781</v>
+        <v>81.69999694824219</v>
       </c>
       <c r="I151" t="n">
-        <v>1.458080140343773</v>
+        <v>1.46878830455797</v>
       </c>
       <c r="J151" t="n">
         <v>17</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>23.29999923706055</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I152" t="n">
-        <v>1.158798321205706</v>
+        <v>1.153846172656299</v>
       </c>
       <c r="J152" t="n">
         <v>17</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>29.85000038146973</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="I154" t="n">
-        <v>1.005025112784367</v>
+        <v>0.9868421176463945</v>
       </c>
       <c r="J154" t="n">
         <v>17</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>0.2010000050067902</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="I155" t="n">
-        <v>3.482586977927451</v>
+        <v>3.499999947845937</v>
       </c>
       <c r="J155" t="n">
         <v>10</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>7.46999979019165</v>
+        <v>7.570000171661377</v>
       </c>
       <c r="I156" t="n">
-        <v>2.141900997240792</v>
+        <v>2.113606292889754</v>
       </c>
       <c r="J156" t="n">
         <v>10</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>2.220000028610229</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I157" t="n">
-        <v>2.927927890194284</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J157" t="n">
         <v>10</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>8.180000305175781</v>
+        <v>8.239999771118164</v>
       </c>
       <c r="I158" t="n">
-        <v>3.056234604805772</v>
+        <v>3.033980666798916</v>
       </c>
       <c r="J158" t="n">
         <v>10</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>7</v>
+        <v>7.010000228881836</v>
       </c>
       <c r="I160" t="n">
-        <v>7.142857142857142</v>
+        <v>7.132667384801997</v>
       </c>
       <c r="J160" t="n">
         <v>3</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>19.04999923706055</v>
+        <v>19.61000061035156</v>
       </c>
       <c r="I161" t="n">
-        <v>3.41207362746486</v>
+        <v>3.314635286940702</v>
       </c>
       <c r="J161" t="n">
         <v>3</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>13.10499954223633</v>
+        <v>13.47999954223633</v>
       </c>
       <c r="I162" t="n">
-        <v>4.120564813906515</v>
+        <v>4.005934854137348</v>
       </c>
       <c r="J162" t="n">
         <v>3</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>6.619999885559082</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I163" t="n">
-        <v>1.510574044240405</v>
+        <v>1.503759376930877</v>
       </c>
       <c r="J163" t="n">
         <v>3</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>9.199999809265137</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I164" t="n">
-        <v>1.739130470838349</v>
+        <v>1.702127728650021</v>
       </c>
       <c r="J164" t="n">
         <v>3</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>312.75</v>
+        <v>321.1000061035156</v>
       </c>
       <c r="I165" t="n">
-        <v>1.155875299760192</v>
+        <v>1.125817480936018</v>
       </c>
       <c r="J165" t="n">
         <v>3</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>31.39999961853027</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="I166" t="n">
-        <v>4.331210243701452</v>
+        <v>4.415584524961806</v>
       </c>
       <c r="J166" t="n">
         <v>3</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>19.43000030517578</v>
+        <v>19.70999908447266</v>
       </c>
       <c r="I167" t="n">
-        <v>29.96191409451104</v>
+        <v>29.53627737398628</v>
       </c>
       <c r="J167" t="n">
         <v>3</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>15.19999980926514</v>
+        <v>15.35999965667725</v>
       </c>
       <c r="I168" t="n">
-        <v>3.848684258820938</v>
+        <v>3.808593835128705</v>
       </c>
       <c r="J168" t="n">
         <v>3</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>19.94499969482422</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="I169" t="n">
-        <v>3.158686435896445</v>
+        <v>3.047895489475763</v>
       </c>
       <c r="J169" t="n">
         <v>3</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>120.6999969482422</v>
+        <v>121.6500015258789</v>
       </c>
       <c r="I170" t="n">
-        <v>0.7456503916780812</v>
+        <v>0.7398273643330294</v>
       </c>
       <c r="J170" t="n">
         <v>3</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>69.04000091552734</v>
+        <v>71.80999755859375</v>
       </c>
       <c r="I171" t="n">
-        <v>2.49246810136265</v>
+        <v>2.396323713276698</v>
       </c>
       <c r="J171" t="n">
         <v>3</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>26.10000038146973</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5363984595931122</v>
+        <v>0.5426356749611693</v>
       </c>
       <c r="J172" t="n">
         <v>-4</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>1.570000052452087</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I173" t="n">
-        <v>3.821655923277815</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J173" t="n">
         <v>-4</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>2.259999990463257</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I174" t="n">
-        <v>1.504424785109431</v>
+        <v>1.574074011525993</v>
       </c>
       <c r="J174" t="n">
         <v>-18</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>23.39999961853027</v>
+        <v>21.76000022888184</v>
       </c>
       <c r="I175" t="n">
-        <v>1.111111129224584</v>
+        <v>1.19485292860845</v>
       </c>
       <c r="J175" t="n">
         <v>-25</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>35.30500030517578</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="I176" t="n">
-        <v>0.2549213970316999</v>
+        <v>0.2418704708798449</v>
       </c>
       <c r="J176" t="n">
         <v>-25</v>
@@ -10464,7 +10464,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10481,7 +10481,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10491,14 +10491,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10508,14 +10508,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10549,7 +10549,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10583,7 +10583,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10600,7 +10600,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10617,7 +10617,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10634,7 +10634,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10644,14 +10644,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10668,7 +10668,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10685,7 +10685,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10702,7 +10702,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10719,7 +10719,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10753,7 +10753,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10770,7 +10770,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10787,7 +10787,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10804,7 +10804,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10821,7 +10821,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10838,7 +10838,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10848,14 +10848,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10872,7 +10872,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10889,7 +10889,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10906,7 +10906,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10923,7 +10923,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10940,7 +10940,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10950,14 +10950,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10974,7 +10974,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10991,7 +10991,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11001,14 +11001,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11025,7 +11025,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11042,7 +11042,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11052,14 +11052,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11069,14 +11069,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11093,7 +11093,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11110,7 +11110,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11127,7 +11127,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11144,7 +11144,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11161,7 +11161,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11178,7 +11178,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11195,7 +11195,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11212,7 +11212,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11222,14 +11222,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11263,7 +11263,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11280,7 +11280,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11297,7 +11297,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11314,7 +11314,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11331,7 +11331,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11348,7 +11348,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11365,7 +11365,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11382,7 +11382,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11433,7 +11433,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11450,7 +11450,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11467,7 +11467,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11477,14 +11477,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11501,7 +11501,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11518,7 +11518,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11535,7 +11535,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11552,7 +11552,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11569,7 +11569,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11586,7 +11586,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11603,7 +11603,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11620,7 +11620,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11630,14 +11630,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11654,7 +11654,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11688,7 +11688,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11705,7 +11705,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11722,7 +11722,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11739,7 +11739,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11756,7 +11756,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11790,7 +11790,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11807,7 +11807,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11824,7 +11824,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11841,7 +11841,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11858,7 +11858,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11868,14 +11868,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11892,7 +11892,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11909,7 +11909,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11919,14 +11919,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11943,7 +11943,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11970,14 +11970,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11994,7 +11994,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12004,14 +12004,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12021,14 +12021,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12045,7 +12045,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12055,14 +12055,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12079,7 +12079,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12096,7 +12096,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12106,14 +12106,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12123,14 +12123,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12147,7 +12147,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12164,7 +12164,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12181,7 +12181,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12198,7 +12198,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12215,7 +12215,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12232,7 +12232,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12242,14 +12242,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12266,7 +12266,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12283,7 +12283,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12293,14 +12293,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12317,7 +12317,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12351,7 +12351,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12368,7 +12368,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12402,7 +12402,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12419,7 +12419,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12436,7 +12436,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12453,7 +12453,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12470,7 +12470,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12487,7 +12487,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12497,14 +12497,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12521,7 +12521,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12538,7 +12538,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12555,7 +12555,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12572,7 +12572,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12589,7 +12589,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12599,14 +12599,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12616,14 +12616,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12633,14 +12633,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12657,7 +12657,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12691,7 +12691,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12701,14 +12701,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12718,14 +12718,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12735,14 +12735,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12752,14 +12752,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12776,7 +12776,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12793,7 +12793,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12810,7 +12810,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12827,7 +12827,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12844,7 +12844,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12854,14 +12854,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12878,7 +12878,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12895,7 +12895,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12912,7 +12912,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12929,7 +12929,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12946,7 +12946,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12956,14 +12956,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12980,7 +12980,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12997,7 +12997,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13014,7 +13014,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13031,7 +13031,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13041,14 +13041,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13065,7 +13065,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13082,7 +13082,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13099,7 +13099,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13116,7 +13116,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13133,7 +13133,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13160,14 +13160,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13194,14 +13194,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13218,7 +13218,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13235,7 +13235,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13252,7 +13252,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13269,7 +13269,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13320,7 +13320,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13337,7 +13337,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13354,7 +13354,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13364,14 +13364,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13405,7 +13405,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13422,7 +13422,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13439,7 +13439,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13456,7 +13456,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13473,7 +13473,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13490,7 +13490,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13507,7 +13507,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13517,14 +13517,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13534,14 +13534,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13551,14 +13551,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13575,7 +13575,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13585,14 +13585,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13609,7 +13609,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13626,7 +13626,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13643,7 +13643,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13660,7 +13660,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13677,7 +13677,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13694,7 +13694,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13711,7 +13711,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13728,7 +13728,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13745,7 +13745,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13755,14 +13755,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13779,7 +13779,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13796,7 +13796,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13830,7 +13830,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13847,7 +13847,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13864,7 +13864,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13881,7 +13881,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13898,7 +13898,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13915,7 +13915,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13932,7 +13932,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13942,14 +13942,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13966,7 +13966,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13976,14 +13976,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14000,7 +14000,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14017,7 +14017,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14034,7 +14034,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14051,7 +14051,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14068,7 +14068,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14085,7 +14085,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14095,14 +14095,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14119,7 +14119,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14136,7 +14136,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14153,7 +14153,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14180,14 +14180,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14197,14 +14197,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14221,7 +14221,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14238,7 +14238,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14255,7 +14255,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14272,7 +14272,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14289,7 +14289,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14306,7 +14306,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14323,7 +14323,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14340,7 +14340,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14357,7 +14357,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14391,7 +14391,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14408,7 +14408,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14425,7 +14425,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14442,7 +14442,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14459,7 +14459,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14476,7 +14476,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14510,7 +14510,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14527,7 +14527,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14544,7 +14544,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14554,14 +14554,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14578,7 +14578,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14588,14 +14588,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14612,7 +14612,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14629,7 +14629,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14646,7 +14646,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14663,7 +14663,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14697,7 +14697,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14714,7 +14714,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14724,14 +14724,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14741,14 +14741,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14758,14 +14758,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14775,14 +14775,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14799,7 +14799,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14833,7 +14833,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14843,14 +14843,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14867,7 +14867,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14901,7 +14901,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14911,14 +14911,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14952,7 +14952,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14969,7 +14969,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14979,14 +14979,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15003,7 +15003,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15020,7 +15020,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15037,7 +15037,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15047,14 +15047,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15105,7 +15105,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15122,7 +15122,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15132,14 +15132,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15149,14 +15149,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15166,14 +15166,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15183,14 +15183,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15207,7 +15207,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15224,7 +15224,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15234,14 +15234,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15258,7 +15258,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15268,14 +15268,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15285,14 +15285,14 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15309,7 +15309,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15319,14 +15319,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15336,14 +15336,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15353,14 +15353,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15377,7 +15377,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15387,14 +15387,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15411,7 +15411,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15421,14 +15421,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15445,7 +15445,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15462,7 +15462,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15472,14 +15472,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15489,14 +15489,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15513,7 +15513,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15523,14 +15523,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15547,7 +15547,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15557,14 +15557,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15574,14 +15574,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15591,14 +15591,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15608,14 +15608,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15625,14 +15625,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15642,14 +15642,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15666,7 +15666,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15676,14 +15676,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15693,14 +15693,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15717,7 +15717,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15727,14 +15727,14 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15744,14 +15744,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15768,7 +15768,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15785,7 +15785,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15795,14 +15795,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15812,14 +15812,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15836,7 +15836,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15853,7 +15853,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15887,7 +15887,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15904,7 +15904,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15914,14 +15914,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15931,14 +15931,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15955,7 +15955,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15965,14 +15965,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15989,7 +15989,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16016,14 +16016,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16033,14 +16033,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16050,14 +16050,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16067,14 +16067,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16084,14 +16084,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16101,14 +16101,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16125,7 +16125,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16135,14 +16135,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16152,14 +16152,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16169,14 +16169,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16186,14 +16186,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16203,14 +16203,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16227,7 +16227,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16237,14 +16237,14 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16261,7 +16261,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16271,14 +16271,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16295,7 +16295,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16305,14 +16305,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16329,7 +16329,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16339,14 +16339,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16356,14 +16356,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16373,14 +16373,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16397,7 +16397,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16407,14 +16407,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16431,7 +16431,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16441,14 +16441,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16458,14 +16458,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16475,14 +16475,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16492,14 +16492,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16509,14 +16509,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16533,7 +16533,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16543,14 +16543,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16560,14 +16560,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16577,14 +16577,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16594,14 +16594,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16618,7 +16618,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16635,7 +16635,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16645,14 +16645,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16662,14 +16662,14 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16679,14 +16679,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16703,7 +16703,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16713,14 +16713,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16730,14 +16730,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16747,14 +16747,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16764,14 +16764,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16781,14 +16781,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16805,7 +16805,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16822,7 +16822,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16839,7 +16839,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16849,14 +16849,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16866,14 +16866,14 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16890,7 +16890,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16917,14 +16917,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16941,7 +16941,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16951,14 +16951,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16975,7 +16975,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16985,14 +16985,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17002,14 +17002,14 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17019,14 +17019,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17036,14 +17036,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17060,7 +17060,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17077,7 +17077,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17087,14 +17087,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17111,7 +17111,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17128,7 +17128,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17145,7 +17145,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17162,7 +17162,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17172,14 +17172,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17196,7 +17196,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17213,7 +17213,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17230,7 +17230,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17240,14 +17240,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17264,7 +17264,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17274,14 +17274,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17291,14 +17291,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17315,7 +17315,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17400,7 +17400,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17417,7 +17417,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17434,7 +17434,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17451,7 +17451,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17461,14 +17461,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17478,14 +17478,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17495,14 +17495,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17512,14 +17512,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17553,7 +17553,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17563,14 +17563,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17587,7 +17587,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17597,14 +17597,14 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17621,7 +17621,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17631,14 +17631,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17655,7 +17655,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17665,14 +17665,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17689,7 +17689,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17706,7 +17706,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17716,14 +17716,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17733,14 +17733,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17750,14 +17750,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17767,14 +17767,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17791,7 +17791,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17801,14 +17801,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17818,14 +17818,14 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17835,14 +17835,14 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17859,7 +17859,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17876,7 +17876,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17893,7 +17893,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17903,14 +17903,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17927,7 +17927,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17944,7 +17944,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17961,7 +17961,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17978,7 +17978,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17988,14 +17988,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18012,7 +18012,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18029,7 +18029,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18046,7 +18046,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18063,7 +18063,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18080,7 +18080,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18090,14 +18090,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18114,7 +18114,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18124,14 +18124,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18148,7 +18148,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18158,14 +18158,14 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18182,7 +18182,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18192,14 +18192,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18216,7 +18216,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18233,7 +18233,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18243,14 +18243,14 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18260,14 +18260,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18277,14 +18277,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18301,7 +18301,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18318,7 +18318,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18328,14 +18328,14 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18345,14 +18345,14 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18362,14 +18362,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18396,14 +18396,14 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18420,7 +18420,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18437,7 +18437,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18454,7 +18454,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18464,14 +18464,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18481,14 +18481,14 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18505,7 +18505,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18522,7 +18522,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18539,7 +18539,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18556,7 +18556,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18566,14 +18566,14 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18590,7 +18590,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18607,7 +18607,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18617,14 +18617,14 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18641,7 +18641,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18658,7 +18658,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18668,14 +18668,14 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18692,7 +18692,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18702,14 +18702,14 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18719,14 +18719,14 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18736,14 +18736,14 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18753,14 +18753,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18777,7 +18777,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18794,7 +18794,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18804,14 +18804,14 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18821,14 +18821,14 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18838,14 +18838,14 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18862,7 +18862,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18879,7 +18879,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18896,7 +18896,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18913,7 +18913,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18930,7 +18930,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18940,14 +18940,14 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -18964,7 +18964,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -18981,7 +18981,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18998,7 +18998,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -19015,7 +19015,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -19032,7 +19032,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -19049,7 +19049,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -19066,7 +19066,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -19083,7 +19083,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -19093,14 +19093,14 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -19110,14 +19110,14 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -19127,14 +19127,14 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19144,14 +19144,14 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19161,14 +19161,14 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19178,14 +19178,14 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19195,14 +19195,14 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19219,7 +19219,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -19229,14 +19229,14 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -19253,7 +19253,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -19270,7 +19270,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19280,14 +19280,14 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19304,7 +19304,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -19321,7 +19321,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19338,7 +19338,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19348,14 +19348,14 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19372,7 +19372,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19382,14 +19382,14 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19399,14 +19399,14 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19423,7 +19423,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19467,14 +19467,14 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19491,7 +19491,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -19501,14 +19501,14 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19518,14 +19518,14 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19535,14 +19535,14 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19559,7 +19559,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -19569,14 +19569,14 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -19601,146 +19601,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NL0015000LU4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-04-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>19.43000030517578</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.8216</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>29.96191409451104</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Svas Biosana S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005469264</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>8.979999542236328</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.227171605736999</v>
-      </c>
-      <c r="I3" t="n">
-        <v>45</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19751,61 +19614,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Valica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>